--- a/medical_application_forms/038_sports_medicine_partnership_application_form--medical_application_forms.xlsx
+++ b/medical_application_forms/038_sports_medicine_partnership_application_form--medical_application_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1033,8 +1033,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="27" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="17" customWidth="1" min="2" max="2"/>
+    <col width="17" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1062,12 +1062,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'name':_'phone',_'label':_'phone'}</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'name': 'phone', 'label': 'Phone'}</t>
+          <t>Phone</t>
         </is>
       </c>
     </row>
@@ -1079,12 +1079,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'name':_'email',_'label':_'email'}</t>
+          <t>email</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'name': 'email', 'label': 'Email'}</t>
+          <t>Email</t>
         </is>
       </c>
     </row>
@@ -1096,12 +1096,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'name':_'sports_medicine',_'label':_'sports_medicine'}</t>
+          <t>sports_medicine</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'name': 'sports_medicine', 'label': 'Sports Medicine'}</t>
+          <t>Sports Medicine</t>
         </is>
       </c>
     </row>
@@ -1113,12 +1113,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'name':_'physiotherapy',_'label':_'physiotherapy'}</t>
+          <t>physiotherapy</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'name': 'physiotherapy', 'label': 'Physiotherapy'}</t>
+          <t>Physiotherapy</t>
         </is>
       </c>
     </row>
@@ -1130,12 +1130,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'name':_'other',_'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'name': 'other', 'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1147,12 +1147,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'name':_'bank_transfer',_'label':_'bank_transfer'}</t>
+          <t>bank_transfer</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'name': 'bank_transfer', 'label': 'Bank Transfer'}</t>
+          <t>Bank Transfer</t>
         </is>
       </c>
     </row>
@@ -1164,12 +1164,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'name':_'check',_'label':_'check'}</t>
+          <t>check</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'name': 'check', 'label': 'Check'}</t>
+          <t>Check</t>
         </is>
       </c>
     </row>
@@ -1181,12 +1181,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'name':_'other',_'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'name': 'other', 'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1232,12 +1232,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'name':_'pdf',_'label':_'pdf'}</t>
+          <t>pdf</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'name': 'pdf', 'label': 'PDF'}</t>
+          <t>PDF</t>
         </is>
       </c>
     </row>
@@ -1249,12 +1249,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'name':_'docx',_'label':_'docx'}</t>
+          <t>docx</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'name': 'docx', 'label': 'Docx'}</t>
+          <t>Docx</t>
         </is>
       </c>
     </row>
@@ -1266,12 +1266,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'name':_'excel',_'label':_'excel'}</t>
+          <t>excel</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'name': 'excel', 'label': 'Excel'}</t>
+          <t>Excel</t>
         </is>
       </c>
     </row>
